--- a/data/trans_camb/IQ2605_R2-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IQ2605_R2-Habitat-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>35,98</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>36,56</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>30,45</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>30,26</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>17,53</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>24,84</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>35,98</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>36,56</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>29,58</t>
+          <t>24,58</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>27,23</t>
+          <t>27,64</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>21,58; 39,07</t>
+          <t>26,63; 44,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,92; 26,85</t>
+          <t>27,89; 45,69</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9,82; 38,54</t>
+          <t>14,65; 44,72</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27,57; 44,15</t>
+          <t>20,56; 38,93</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>28,1; 44,57</t>
+          <t>7,63; 26,7</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,93; 43,97</t>
+          <t>9,84; 38,09</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,14; 38,94</t>
+          <t>26,75; 39,43</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>20,95; 34,1</t>
+          <t>20,24; 33,77</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>16,19; 37,16</t>
+          <t>16,58; 37,95</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>86,54%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>87,94%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>73,23%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>62,13%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>36,0%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>51,01%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>86,54%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>87,94%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>71,15%</t>
+          <t>50,48%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>60,57%</t>
+          <t>61,48%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>40,12; 93,05</t>
+          <t>56,99; 122,87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12,96; 62,14</t>
+          <t>57,42; 125,92</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20,16; 87,37</t>
+          <t>32,95; 121,9</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>58,47; 122,9</t>
+          <t>38,04; 91,94</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>60,29; 124,88</t>
+          <t>14,54; 61,56</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,9; 122,75</t>
+          <t>20,3; 87,06</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>53,63; 95,06</t>
+          <t>54,51; 96,48</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>42,58; 81,11</t>
+          <t>41,42; 82,27</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>33,8; 87,5</t>
+          <t>35,84; 90,87</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>20,03</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>20,32</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>30,39</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>27,37</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>25,87</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>25,75</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>20,03</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>20,32</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>30,66</t>
+          <t>25,71</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>29,3</t>
+          <t>28,96</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>19,63; 33,95</t>
+          <t>13,29; 26,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>19,09; 32,57</t>
+          <t>13,57; 27,48</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12,48; 38,51</t>
+          <t>20,54; 39,12</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12,99; 27,72</t>
+          <t>20,24; 34,55</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13,46; 27,0</t>
+          <t>17,78; 33,07</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19,09; 38,47</t>
+          <t>10,75; 37,01</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,18; 28,05</t>
+          <t>18,16; 28,8</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>17,67; 27,86</t>
+          <t>18,15; 28,76</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>20,29; 35,88</t>
+          <t>19,74; 35,26</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>34,79%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>35,3%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>52,8%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>52,84%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>49,94%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>49,71%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>34,79%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>35,3%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>53,28%</t>
+          <t>49,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>53,47%</t>
+          <t>52,85%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>34,12; 72,21</t>
+          <t>21,81; 50,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>34,13; 69,35</t>
+          <t>22,3; 52,05</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23,04; 77,75</t>
+          <t>34,12; 73,03</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>21,14; 52,97</t>
+          <t>36,08; 72,88</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>21,53; 51,08</t>
+          <t>30,59; 69,86</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,59; 71,98</t>
+          <t>20,56; 76,45</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,8; 53,29</t>
+          <t>31,95; 56,44</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>29,57; 53,33</t>
+          <t>31,36; 55,97</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>35,32; 68,51</t>
+          <t>35,57; 66,67</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>26,69</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>40,18</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>23,15</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>17,77</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>33,72</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>15,78</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>26,69</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>40,18</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>22,48</t>
+          <t>12,48</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>19,36</t>
+          <t>18,46</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,77; 26,36</t>
+          <t>18,59; 35,51</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>25,5; 40,88</t>
+          <t>32,14; 47,19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 31,51</t>
+          <t>7,88; 36,7</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18,63; 35,86</t>
+          <t>9,04; 25,58</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>31,7; 48,17</t>
+          <t>25,78; 41,61</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,37; 36,21</t>
+          <t>-4,63; 28,8</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,14; 28,23</t>
+          <t>16,47; 29,1</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>31,2; 43,08</t>
+          <t>31,72; 43,28</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,34; 29,51</t>
+          <t>7,81; 28,61</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>58,45%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>88,01%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>50,7%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>34,73%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>65,9%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>30,84%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>58,45%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>88,01%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>49,24%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>40,07%</t>
+          <t>38,21%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>15,75; 58,08</t>
+          <t>36,35; 87,13</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>44,75; 90,21</t>
+          <t>62,45; 116,83</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,29; 68,0</t>
+          <t>15,71; 86,89</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>37,75; 90,48</t>
+          <t>15,76; 55,61</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>60,91; 123,05</t>
+          <t>44,58; 90,93</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>11,84; 87,29</t>
+          <t>-8,88; 59,69</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>31,32; 63,07</t>
+          <t>31,98; 66,57</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>58,6; 97,05</t>
+          <t>60,27; 98,2</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>16,94; 65,12</t>
+          <t>14,82; 63,02</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>4,97</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>14,81</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>10,22</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>6,8</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>12,83</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>8,28</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>4,97</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>14,81</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,38</t>
+          <t>7,95</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>9,88</t>
+          <t>9,09</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 14,97</t>
+          <t>-2,64; 13,31</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,86; 20,16</t>
+          <t>7,41; 22,46</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,21; 19,22</t>
+          <t>-4,86; 22,58</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 13,37</t>
+          <t>-1,33; 14,42</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,21; 22,31</t>
+          <t>4,52; 20,68</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 22,84</t>
+          <t>-6,09; 19,12</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,07; 11,37</t>
+          <t>0,21; 11,75</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>8,57; 19,27</t>
+          <t>8,13; 19,19</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,13; 18,02</t>
+          <t>-0,86; 17,23</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>8,13%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>24,25%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>16,73%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>11,13%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>20,99%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>13,54%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>8,13%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>24,25%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>14,87%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 26,28</t>
+          <t>-4,06; 23,75</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>7,51; 34,96</t>
+          <t>11,63; 40,38</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-8,3; 32,67</t>
+          <t>-7,62; 38,24</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 23,49</t>
+          <t>-2,11; 25,62</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>11,33; 39,65</t>
+          <t>6,84; 37,32</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-5,88; 38,81</t>
+          <t>-9,38; 33,11</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,11; 19,45</t>
+          <t>0,22; 19,93</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>13,2; 33,12</t>
+          <t>12,51; 33,28</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,49; 30,68</t>
+          <t>-1,45; 29,14</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>20,39</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>26,33</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>23,5</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>19,66</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>22,07</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>17,97</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>20,39</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>26,33</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>23,52</t>
+          <t>17,28</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>21,08</t>
+          <t>20,72</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>15,42; 23,83</t>
+          <t>16,46; 23,92</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>18,16; 26,21</t>
+          <t>22,41; 29,82</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>11,12; 24,55</t>
+          <t>16,5; 29,61</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>15,86; 24,16</t>
+          <t>14,95; 23,58</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>21,8; 30,24</t>
+          <t>17,88; 25,94</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>16,6; 29,91</t>
+          <t>10,04; 24,29</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17,24; 23,07</t>
+          <t>17,28; 23,12</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>21,38; 27,05</t>
+          <t>21,7; 27,12</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>16,78; 25,71</t>
+          <t>15,52; 25,44</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>38,58%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>49,83%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>44,47%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>36,43%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>40,9%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>33,3%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>38,58%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>49,83%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>44,52%</t>
+          <t>32,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>39,5%</t>
+          <t>38,82%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>27,33; 46,42</t>
+          <t>29,64; 47,61</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>31,96; 51,59</t>
+          <t>40,71; 59,33</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>20,07; 46,64</t>
+          <t>30,52; 57,89</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>28,42; 48,02</t>
+          <t>26,63; 46,15</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>39,74; 59,9</t>
+          <t>31,9; 50,8</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>31,1; 58,53</t>
+          <t>18,31; 46,55</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>31,49; 44,79</t>
+          <t>31,36; 44,54</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>38,5; 52,0</t>
+          <t>39,46; 52,87</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>30,61; 49,25</t>
+          <t>28,4; 49,1</t>
         </is>
       </c>
     </row>
